--- a/workflows/docs/bulkSubmission/WasteWater-EDGE-BulkSubmission.xlsx
+++ b/workflows/docs/bulkSubmission/WasteWater-EDGE-BulkSubmission.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="11109"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10208"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/yxu/dev/node20-projects/edge-core/workflows/docs/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/yxu/dev/edge-github/wastewater-edge/workflows/docs/bulkSubmission/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E805971A-11D0-D34A-A35E-3B67CF40DAD6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0D006481-C54B-2F49-853C-6D44F64A644F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="6360" yWindow="2860" windowWidth="27240" windowHeight="16440" xr2:uid="{D4B1EDC8-DFE1-D14C-9E75-173BCE7BAFAC}"/>
   </bookViews>
@@ -46,13 +46,13 @@
     <t>Sample Id</t>
   </si>
   <si>
-    <t>Workflow</t>
-  </si>
-  <si>
     <t>R2</t>
   </si>
   <si>
     <t>R1 or Long Reads</t>
+  </si>
+  <si>
+    <t>Sequencing</t>
   </si>
 </sst>
 </file>
@@ -440,13 +440,13 @@
         <v>0</v>
       </c>
       <c r="C1" t="s">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="D1" t="s">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="E1" t="s">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
   </sheetData>
@@ -462,7 +462,7 @@
       <formula2>30</formula2>
     </dataValidation>
     <dataValidation allowBlank="1" showInputMessage="1" showErrorMessage="1" promptTitle="Description" prompt="Optional" sqref="B2:B97" xr:uid="{CB3D86F2-D212-C340-9296-8EF1CAF1D742}"/>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" errorTitle="Workflow" error="Select from dropdown list" promptTitle="Workflow" prompt="Default: metaG" sqref="C2:C106" xr:uid="{CBEA70A8-438C-B741-BF37-86C351AB6956}">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" errorTitle="Sequencing" error="Select from dropdown list" promptTitle="Sequencing" prompt="Default: metaG" sqref="C2:C106" xr:uid="{CBEA70A8-438C-B741-BF37-86C351AB6956}">
       <formula1>"metaG, metaT"</formula1>
     </dataValidation>
   </dataValidations>
